--- a/ALNY.xlsx
+++ b/ALNY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC5A9C7-2D89-4E13-B38F-5F9CDF9F18A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE91D83B-9929-4494-BDE1-E21032EA4AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36190" yWindow="2280" windowWidth="23410" windowHeight="16240" activeTab="1" xr2:uid="{7C34F31A-DE2D-4EBA-93CC-6997970EE8B3}"/>
+    <workbookView xWindow="14690" yWindow="2940" windowWidth="22360" windowHeight="16580" xr2:uid="{7C34F31A-DE2D-4EBA-93CC-6997970EE8B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="154">
   <si>
     <t>Price</t>
   </si>
@@ -376,9 +376,6 @@
     <t>9/19/22: RNAi roundtable webcast</t>
   </si>
   <si>
-    <t>IgAN</t>
-  </si>
-  <si>
     <t>Alzheimer's, CAA</t>
   </si>
   <si>
@@ -488,6 +485,42 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>ALN-6400</t>
+  </si>
+  <si>
+    <t>HHT</t>
+  </si>
+  <si>
+    <t>ALN-2232</t>
+  </si>
+  <si>
+    <t>ACVR1C</t>
+  </si>
+  <si>
+    <t>IgAN, gMG</t>
+  </si>
+  <si>
+    <t>C5?</t>
+  </si>
+  <si>
+    <t>Hypertension</t>
+  </si>
+  <si>
+    <t>II</t>
   </si>
 </sst>
 </file>
@@ -631,7 +664,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -675,6 +708,7 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -699,14 +733,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>21828</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>25796</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>21828</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>25796</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>148829</xdr:rowOff>
     </xdr:to>
@@ -723,8 +757,58 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16674703" y="0"/>
-          <a:ext cx="0" cy="7316392"/>
+          <a:off x="19929077" y="0"/>
+          <a:ext cx="0" cy="6990954"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>27781</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>35719</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>27781</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A33746B-26D8-AF71-081F-6D2B67E4075D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30388719" y="35719"/>
+          <a:ext cx="0" cy="5814219"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1061,16 +1145,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C2D40B6-A1FF-428A-9D75-C1B382F99280}">
-  <dimension ref="B2:M28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:M30"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
@@ -1096,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="23" t="s">
         <v>50</v>
       </c>
@@ -1120,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>130.31100000000001</v>
+        <v>133.512573</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>51</v>
       </c>
@@ -1136,11 +1220,11 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>40266.099000000002</v>
+        <v>51001.802885999998</v>
       </c>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="23" t="s">
         <v>52</v>
       </c>
@@ -1161,14 +1245,14 @@
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <f>1019.654+1605.368+7.2</f>
-        <v>2632.2219999999998</v>
+        <f>1710.779+1298.444</f>
+        <v>3009.223</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>53</v>
       </c>
@@ -1189,13 +1273,13 @@
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>1025.566</v>
+        <v>1009.372</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
         <v>48</v>
       </c>
@@ -1216,188 +1300,215 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>38659.442999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+        <v>49001.951886000003</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="9"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>150</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>151</v>
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H10" s="5"/>
       <c r="J10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" t="s">
+        <v>153</v>
       </c>
       <c r="H11" s="5"/>
       <c r="J11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H12" s="5"/>
       <c r="J12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="H13" s="5"/>
       <c r="J13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="H14" s="5"/>
       <c r="J14" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="H15" s="5"/>
       <c r="J15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B16" s="4"/>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="C16" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" t="s">
+        <v>111</v>
+      </c>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="4"/>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="6"/>
+      <c r="C19" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="E16" t="s">
-        <v>120</v>
-      </c>
-      <c r="F16" t="s">
-        <v>112</v>
-      </c>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="6"/>
-      <c r="C17" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="E19" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G27" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G22" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G25" t="s">
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G26" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G29" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G27" t="s">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G30" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="G28" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1413,20 +1524,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26819CA-CB58-43F1-B61F-985A61CFCF16}">
-  <dimension ref="A1:AT24"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AX24"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="9.140625" style="12"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="18" width="9.1796875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="C2" s="12" t="s">
         <v>19</v>
       </c>
@@ -1476,94 +1587,106 @@
         <v>33</v>
       </c>
       <c r="S2" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="T2" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="U2" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="V2" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="W2" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="X2" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="Y2" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="X2" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Z2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="Z2" s="12" t="s">
-        <v>136</v>
-      </c>
       <c r="AA2" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB2" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AC2" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AD2" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AE2" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="AH2">
+      <c r="AF2" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="AG2" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="AH2" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="AL2">
         <v>2015</v>
       </c>
-      <c r="AI2">
-        <f>+AH2+1</f>
+      <c r="AM2">
+        <f>+AL2+1</f>
         <v>2016</v>
       </c>
-      <c r="AJ2">
-        <f t="shared" ref="AJ2:AT2" si="0">+AI2+1</f>
+      <c r="AN2">
+        <f t="shared" ref="AN2:AX2" si="0">+AM2+1</f>
         <v>2017</v>
       </c>
-      <c r="AK2">
+      <c r="AO2">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="AL2">
+      <c r="AP2">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="AM2">
+      <c r="AQ2">
         <f t="shared" si="0"/>
         <v>2020</v>
       </c>
-      <c r="AN2">
+      <c r="AR2">
         <f t="shared" si="0"/>
         <v>2021</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
     </row>
-    <row r="3" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1613,6 +1736,9 @@
       <c r="U3" s="2">
         <v>81.588999999999999</v>
       </c>
+      <c r="V3" s="2">
+        <v>79.006</v>
+      </c>
       <c r="W3" s="2">
         <v>69.216999999999999</v>
       </c>
@@ -1629,35 +1755,51 @@
         <v>49</v>
       </c>
       <c r="AB3" s="2">
-        <f>+AA3-1</f>
-        <v>48</v>
+        <v>52.537999999999997</v>
       </c>
       <c r="AC3" s="2">
-        <f>+AB3-1</f>
-        <v>47</v>
+        <v>39.075000000000003</v>
       </c>
       <c r="AD3" s="2">
-        <f>+AC3-1</f>
-        <v>46</v>
-      </c>
-      <c r="AO3" s="2">
-        <f t="shared" ref="AO3:AO8" si="1">SUM(O3:R3)</f>
+        <v>31.687000000000001</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>20.481000000000002</v>
+      </c>
+      <c r="AF3" s="2">
+        <f>+AE3-1</f>
+        <v>19.481000000000002</v>
+      </c>
+      <c r="AG3" s="2">
+        <f>+AF3-1</f>
+        <v>18.481000000000002</v>
+      </c>
+      <c r="AH3" s="2">
+        <f>+AG3-1</f>
+        <v>17.481000000000002</v>
+      </c>
+      <c r="AS3" s="2">
+        <f t="shared" ref="AS3:AS8" si="1">SUM(O3:R3)</f>
         <v>580.33699999999999</v>
       </c>
-      <c r="AP3" s="2">
-        <f>+AO3*0.8</f>
+      <c r="AT3" s="2">
+        <f>+AS3*0.8</f>
         <v>464.26960000000003</v>
       </c>
-      <c r="AQ3" s="2">
-        <f>+AP3*0.8</f>
-        <v>371.41568000000007</v>
-      </c>
-      <c r="AR3" s="2">
-        <f>+AQ3*0.8</f>
-        <v>297.13254400000005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU3" s="2">
+        <f>SUM(W3:Z3)</f>
+        <v>252.75400000000002</v>
+      </c>
+      <c r="AV3" s="2">
+        <f>SUM(AA3:AD3)</f>
+        <v>172.3</v>
+      </c>
+      <c r="AW3" s="2">
+        <f>SUM(AE3:AH3)</f>
+        <v>75.924000000000007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>96</v>
       </c>
@@ -1690,6 +1832,9 @@
       <c r="U4" s="2">
         <v>148.68</v>
       </c>
+      <c r="V4" s="2">
+        <v>175.25399999999999</v>
+      </c>
       <c r="W4" s="2">
         <v>195.24100000000001</v>
       </c>
@@ -1706,32 +1851,50 @@
         <v>310</v>
       </c>
       <c r="AB4" s="2">
-        <f>+W4*1.5</f>
-        <v>292.86150000000004</v>
+        <v>491.95299999999997</v>
       </c>
       <c r="AC4" s="2">
-        <f>+X4*1.5</f>
-        <v>345.1635</v>
+        <v>685.303</v>
       </c>
       <c r="AD4" s="2">
-        <f>+Y4*1.5</f>
-        <v>387.88499999999999</v>
-      </c>
-      <c r="AO4" s="2">
+        <v>826.58799999999997</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>889.93100000000004</v>
+      </c>
+      <c r="AF4" s="2">
+        <f>+AE4+50</f>
+        <v>939.93100000000004</v>
+      </c>
+      <c r="AG4" s="2">
+        <f>+AF4+50</f>
+        <v>989.93100000000004</v>
+      </c>
+      <c r="AH4" s="2">
+        <f>+AG4+50</f>
+        <v>1039.931</v>
+      </c>
+      <c r="AS4" s="2">
         <f t="shared" si="1"/>
         <v>40.228999999999999</v>
       </c>
-      <c r="AP4" s="2">
+      <c r="AT4" s="2">
         <v>200</v>
       </c>
-      <c r="AQ4" s="2">
-        <v>350</v>
-      </c>
-      <c r="AR4" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="5" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU4" s="2">
+        <f>SUM(W4:Z4)</f>
+        <v>970.94</v>
+      </c>
+      <c r="AV4" s="2">
+        <f>SUM(AA4:AD4)</f>
+        <v>2313.8440000000001</v>
+      </c>
+      <c r="AW4" s="2">
+        <f>SUM(AE4:AH4)</f>
+        <v>3859.7240000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1781,6 +1944,9 @@
       <c r="U5" s="2">
         <v>54.148000000000003</v>
       </c>
+      <c r="V5" s="2">
+        <v>59.298000000000002</v>
+      </c>
       <c r="W5" s="2">
         <v>58.055999999999997</v>
       </c>
@@ -1797,35 +1963,51 @@
         <v>67</v>
       </c>
       <c r="AB5" s="2">
-        <f>+AA5-1</f>
-        <v>66</v>
+        <v>80.849000000000004</v>
       </c>
       <c r="AC5" s="2">
-        <f t="shared" ref="AC5:AD5" si="2">+AB5-1</f>
-        <v>65</v>
+        <v>73.873999999999995</v>
       </c>
       <c r="AD5" s="2">
-        <f t="shared" si="2"/>
-        <v>64</v>
-      </c>
-      <c r="AO5" s="2">
+        <v>86.796000000000006</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>74.394000000000005</v>
+      </c>
+      <c r="AF5" s="2">
+        <f>+AB5</f>
+        <v>80.849000000000004</v>
+      </c>
+      <c r="AG5" s="2">
+        <f t="shared" ref="AG5:AG7" si="2">+AC5</f>
+        <v>73.873999999999995</v>
+      </c>
+      <c r="AH5" s="2">
+        <f t="shared" ref="AH5:AH7" si="3">+AD5</f>
+        <v>86.796000000000006</v>
+      </c>
+      <c r="AS5" s="2">
         <f t="shared" si="1"/>
         <v>175.74499999999998</v>
       </c>
-      <c r="AP5" s="2">
-        <f t="shared" ref="AP5:AR6" si="3">+AO5*1.15</f>
+      <c r="AT5" s="2">
+        <f t="shared" ref="AT5:AV6" si="4">+AS5*1.15</f>
         <v>202.10674999999995</v>
       </c>
-      <c r="AQ5" s="2">
-        <f t="shared" si="3"/>
-        <v>232.42276249999992</v>
-      </c>
-      <c r="AR5" s="2">
-        <f t="shared" si="3"/>
-        <v>267.28617687499991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU5" s="2">
+        <f>SUM(W5:Z5)</f>
+        <v>256.226</v>
+      </c>
+      <c r="AV5" s="2">
+        <f>SUM(AA5:AD5)</f>
+        <v>308.51900000000001</v>
+      </c>
+      <c r="AW5" s="2">
+        <f>SUM(AE5:AH5)</f>
+        <v>315.91300000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
@@ -1875,6 +2057,9 @@
       <c r="U6" s="2">
         <v>28.736000000000001</v>
       </c>
+      <c r="V6" s="2">
+        <v>32.729999999999997</v>
+      </c>
       <c r="W6" s="2">
         <v>42.649000000000001</v>
       </c>
@@ -1891,35 +2076,51 @@
         <v>42</v>
       </c>
       <c r="AB6" s="2">
-        <f t="shared" ref="AB6:AD6" si="4">+AA6-1</f>
-        <v>41</v>
+        <v>46.872</v>
       </c>
       <c r="AC6" s="2">
-        <f t="shared" si="4"/>
-        <v>40</v>
+        <v>52.83</v>
       </c>
       <c r="AD6" s="2">
-        <f t="shared" si="4"/>
-        <v>39</v>
-      </c>
-      <c r="AO6" s="2">
+        <v>49.646000000000001</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>51.320999999999998</v>
+      </c>
+      <c r="AF6" s="2">
+        <f t="shared" ref="AF6:AF7" si="5">+AB6</f>
+        <v>46.872</v>
+      </c>
+      <c r="AG6" s="2">
+        <f t="shared" si="2"/>
+        <v>52.83</v>
+      </c>
+      <c r="AH6" s="2">
+        <f t="shared" si="3"/>
+        <v>49.646000000000001</v>
+      </c>
+      <c r="AS6" s="2">
         <f t="shared" si="1"/>
         <v>65.381</v>
       </c>
-      <c r="AP6" s="2">
-        <f t="shared" si="3"/>
+      <c r="AT6" s="2">
+        <f t="shared" si="4"/>
         <v>75.188149999999993</v>
       </c>
-      <c r="AQ6" s="2">
-        <f t="shared" si="3"/>
-        <v>86.466372499999991</v>
-      </c>
-      <c r="AR6" s="2">
-        <f t="shared" si="3"/>
-        <v>99.436328374999988</v>
-      </c>
-    </row>
-    <row r="7" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU6" s="2">
+        <f>SUM(W6:Z6)</f>
+        <v>167.477</v>
+      </c>
+      <c r="AV6" s="2">
+        <f>SUM(AA6:AD6)</f>
+        <v>191.34800000000001</v>
+      </c>
+      <c r="AW6" s="2">
+        <f>SUM(AE6:AH6)</f>
+        <v>200.66899999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
@@ -1966,6 +2167,9 @@
       <c r="T7" s="2">
         <v>5.8440000000000003</v>
       </c>
+      <c r="V7" s="2">
+        <v>76.406999999999996</v>
+      </c>
       <c r="W7" s="2">
         <v>118.548</v>
       </c>
@@ -1982,24 +2186,52 @@
       <c r="AA7" s="2">
         <v>99.185000000000002</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AB7" s="2">
+        <v>61.496000000000002</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>351.74200000000002</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>40.942999999999998</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>82.075000000000003</v>
+      </c>
+      <c r="AF7" s="2">
+        <f t="shared" si="5"/>
+        <v>61.496000000000002</v>
+      </c>
+      <c r="AG7" s="2">
+        <f>+AF7</f>
+        <v>61.496000000000002</v>
+      </c>
+      <c r="AH7" s="2">
+        <f>+AG7</f>
+        <v>61.496000000000002</v>
+      </c>
+      <c r="AS7" s="2">
         <f t="shared" si="1"/>
         <v>92.563999999999993</v>
       </c>
-      <c r="AP7" s="2">
-        <f>+AO7*0.5</f>
+      <c r="AT7" s="2">
+        <f>+AS7*0.5</f>
         <v>46.281999999999996</v>
       </c>
-      <c r="AQ7" s="2">
-        <f>+AP7*0.5</f>
-        <v>23.140999999999998</v>
-      </c>
-      <c r="AR7" s="2">
-        <f>+AQ7*0.5</f>
-        <v>11.570499999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU7" s="2">
+        <f>SUM(W7:Z7)</f>
+        <v>302.79199999999997</v>
+      </c>
+      <c r="AV7" s="2">
+        <f>SUM(AA7:AD7)</f>
+        <v>553.36599999999999</v>
+      </c>
+      <c r="AW7" s="2">
+        <f>SUM(AE7:AH7)</f>
+        <v>266.56299999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
@@ -2046,6 +2278,9 @@
       <c r="T8" s="2">
         <v>7.2050000000000001</v>
       </c>
+      <c r="V8" s="2">
+        <v>17.023</v>
+      </c>
       <c r="W8" s="2">
         <v>10.622</v>
       </c>
@@ -2062,35 +2297,51 @@
         <v>26.466000000000001</v>
       </c>
       <c r="AB8" s="2">
-        <f>+AA8+1</f>
-        <v>27.466000000000001</v>
+        <v>39.981000000000002</v>
       </c>
       <c r="AC8" s="2">
-        <f>+AB8+1</f>
-        <v>28.466000000000001</v>
+        <v>46.201999999999998</v>
       </c>
       <c r="AD8" s="2">
-        <f>+AC8+1</f>
-        <v>29.466000000000001</v>
-      </c>
-      <c r="AO8" s="2">
+        <v>61.372999999999998</v>
+      </c>
+      <c r="AE8" s="2">
+        <v>48.972999999999999</v>
+      </c>
+      <c r="AF8" s="2">
+        <f t="shared" ref="AF8" si="6">+AB8</f>
+        <v>39.981000000000002</v>
+      </c>
+      <c r="AG8" s="2">
+        <f t="shared" ref="AG8" si="7">+AC8</f>
+        <v>46.201999999999998</v>
+      </c>
+      <c r="AH8" s="2">
+        <f t="shared" ref="AH8" si="8">+AD8</f>
+        <v>61.372999999999998</v>
+      </c>
+      <c r="AS8" s="2">
         <f t="shared" si="1"/>
         <v>8.2040000000000006</v>
       </c>
-      <c r="AP8" s="2">
-        <f>+AO8*2</f>
+      <c r="AT8" s="2">
+        <f>+AS8*2</f>
         <v>16.408000000000001</v>
       </c>
-      <c r="AQ8" s="2">
-        <f>+AP8*2</f>
-        <v>32.816000000000003</v>
-      </c>
-      <c r="AR8" s="2">
-        <f>+AQ8*2</f>
-        <v>65.632000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:46" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU8" s="2">
+        <f>SUM(W8:Z8)</f>
+        <v>91.793999999999997</v>
+      </c>
+      <c r="AV8" s="2">
+        <f>SUM(AA8:AD8)</f>
+        <v>174.02199999999999</v>
+      </c>
+      <c r="AW8" s="2">
+        <f>SUM(AE8:AH8)</f>
+        <v>196.529</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" s="17" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B9" s="17" t="s">
         <v>18</v>
       </c>
@@ -2101,111 +2352,131 @@
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18">
-        <f t="shared" ref="I9:P9" si="5">SUM(I3:I8)</f>
+        <f t="shared" ref="I9:P9" si="9">SUM(I3:I8)</f>
         <v>125.85300000000001</v>
       </c>
       <c r="J9" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>163.56199999999998</v>
       </c>
       <c r="K9" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>177.566</v>
       </c>
       <c r="L9" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>220.553</v>
       </c>
       <c r="M9" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>187.63299999999998</v>
       </c>
       <c r="N9" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>258.53500000000003</v>
       </c>
       <c r="O9" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>213.25900000000001</v>
       </c>
       <c r="P9" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>224.81800000000001</v>
       </c>
       <c r="Q9" s="18">
-        <f t="shared" ref="Q9:R9" si="6">SUM(Q3:Q8)</f>
+        <f t="shared" ref="Q9:R9" si="10">SUM(Q3:Q8)</f>
         <v>264.30599999999998</v>
       </c>
       <c r="R9" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>260.077</v>
       </c>
       <c r="S9" s="17">
-        <f t="shared" ref="S9:AA9" si="7">SUM(S3:S8)</f>
+        <f t="shared" ref="S9:AA9" si="11">SUM(S3:S8)</f>
         <v>319.28999999999996</v>
       </c>
       <c r="T9" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>318.75399999999996</v>
       </c>
       <c r="U9" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>313.15300000000002</v>
       </c>
       <c r="V9" s="17">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>439.71800000000002</v>
       </c>
       <c r="W9" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>494.33300000000003</v>
       </c>
       <c r="X9" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>452.39600000000002</v>
       </c>
       <c r="Y9" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>500.91899999999998</v>
       </c>
       <c r="Z9" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>594.33500000000004</v>
       </c>
       <c r="AA9" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>593.65099999999995</v>
       </c>
       <c r="AB9" s="17">
-        <f t="shared" ref="AB9" si="8">SUM(AB3:AB8)</f>
-        <v>475.32750000000004</v>
+        <f t="shared" ref="AB9" si="12">SUM(AB3:AB8)</f>
+        <v>773.68899999999996</v>
       </c>
       <c r="AC9" s="17">
-        <f t="shared" ref="AC9" si="9">SUM(AC3:AC8)</f>
-        <v>525.62950000000001</v>
+        <f t="shared" ref="AC9" si="13">SUM(AC3:AC8)</f>
+        <v>1249.0260000000001</v>
       </c>
       <c r="AD9" s="17">
-        <f t="shared" ref="AD9" si="10">SUM(AD3:AD8)</f>
-        <v>566.351</v>
-      </c>
-      <c r="AO9" s="17">
-        <f>SUM(AO3:AO8)</f>
+        <f t="shared" ref="AD9:AH9" si="14">SUM(AD3:AD8)</f>
+        <v>1097.0330000000001</v>
+      </c>
+      <c r="AE9" s="17">
+        <f t="shared" si="14"/>
+        <v>1167.175</v>
+      </c>
+      <c r="AF9" s="17">
+        <f t="shared" si="14"/>
+        <v>1188.6100000000001</v>
+      </c>
+      <c r="AG9" s="17">
+        <f t="shared" si="14"/>
+        <v>1242.8140000000001</v>
+      </c>
+      <c r="AH9" s="17">
+        <f t="shared" si="14"/>
+        <v>1316.7230000000002</v>
+      </c>
+      <c r="AS9" s="17">
+        <f>SUM(AS3:AS8)</f>
         <v>962.45999999999992</v>
       </c>
-      <c r="AP9" s="17">
-        <f>SUM(AP3:AP8)</f>
+      <c r="AT9" s="17">
+        <f>SUM(AT3:AT8)</f>
         <v>1004.2545</v>
       </c>
-      <c r="AQ9" s="17">
-        <f>SUM(AQ3:AQ8)</f>
-        <v>1096.2618150000001</v>
-      </c>
-      <c r="AR9" s="17">
-        <f>SUM(AR3:AR8)</f>
-        <v>1191.05754925</v>
-      </c>
-    </row>
-    <row r="10" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU9" s="17">
+        <f>SUM(AU3:AU8)</f>
+        <v>2041.9830000000002</v>
+      </c>
+      <c r="AV9" s="17">
+        <f>SUM(AV3:AV8)</f>
+        <v>3713.3990000000003</v>
+      </c>
+      <c r="AW9" s="17">
+        <f>SUM(AW3:AW8)</f>
+        <v>4915.3220000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
@@ -2261,6 +2532,10 @@
         <f>75.336+10.034</f>
         <v>85.37</v>
       </c>
+      <c r="V10" s="2">
+        <f>71.975+13.883</f>
+        <v>85.85799999999999</v>
+      </c>
       <c r="W10" s="2">
         <f>54.613+11.363</f>
         <v>65.975999999999999</v>
@@ -2281,35 +2556,42 @@
         <v>70.183000000000007</v>
       </c>
       <c r="AB10" s="2">
-        <f>+AB9*0.15</f>
-        <v>71.299125000000004</v>
+        <f>142.029+0.924</f>
+        <v>142.953</v>
       </c>
       <c r="AC10" s="2">
-        <f>+AC9*0.15</f>
-        <v>78.844425000000001</v>
+        <f>197.231+2.923</f>
+        <v>200.154</v>
       </c>
       <c r="AD10" s="2">
-        <f>+AD9*0.15</f>
-        <v>84.952649999999991</v>
-      </c>
-      <c r="AO10" s="2">
+        <v>267.72300000000001</v>
+      </c>
+      <c r="AE10" s="2">
+        <f>207.52+3.602</f>
+        <v>211.12200000000001</v>
+      </c>
+      <c r="AS10" s="2">
         <f>SUM(O10:R10)</f>
         <v>157.15509000000003</v>
       </c>
-      <c r="AP10" s="2">
-        <f>+AP9*0.17</f>
+      <c r="AT10" s="2">
+        <f>+AT9*0.17</f>
         <v>170.72326500000003</v>
       </c>
-      <c r="AQ10" s="2">
-        <f>+AQ9*0.17</f>
-        <v>186.36450855000004</v>
-      </c>
-      <c r="AR10" s="2">
-        <f>+AR9*0.17</f>
-        <v>202.47978337250001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU10" s="2">
+        <f>SUM(W10:Z10)</f>
+        <v>323.37</v>
+      </c>
+      <c r="AV10" s="2">
+        <f>SUM(AA10:AD10)</f>
+        <v>681.01300000000003</v>
+      </c>
+      <c r="AW10" s="2">
+        <f>SUM(AE10:AH10)</f>
+        <v>211.12200000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
@@ -2320,35 +2602,35 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16">
-        <f t="shared" ref="I11:P11" si="11">+I9-I10</f>
+        <f t="shared" ref="I11:P11" si="15">+I9-I10</f>
         <v>104.05600000000001</v>
       </c>
       <c r="J11" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>140.53799999999998</v>
       </c>
       <c r="K11" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>146.50400000000002</v>
       </c>
       <c r="L11" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>181.798</v>
       </c>
       <c r="M11" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>154.96999999999997</v>
       </c>
       <c r="N11" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>220.87100000000004</v>
       </c>
       <c r="O11" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>177.63200000000001</v>
       </c>
       <c r="P11" s="16">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>184.01000000000002</v>
       </c>
       <c r="Q11" s="16">
@@ -2360,71 +2642,79 @@
         <v>215.86390999999998</v>
       </c>
       <c r="S11" s="2">
-        <f t="shared" ref="S11:AA11" si="12">+S9-S10</f>
+        <f t="shared" ref="S11:AA11" si="16">+S9-S10</f>
         <v>264.42099999999994</v>
       </c>
       <c r="T11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>233.38399999999996</v>
       </c>
       <c r="U11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>313.15300000000002</v>
       </c>
       <c r="V11" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>353.86</v>
       </c>
       <c r="W11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>428.35700000000003</v>
       </c>
       <c r="X11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>383.72400000000005</v>
       </c>
       <c r="Y11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>415.01400000000001</v>
       </c>
       <c r="Z11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>491.51800000000003</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>523.46799999999996</v>
       </c>
       <c r="AB11" s="2">
         <f>+AB9-AB10</f>
-        <v>404.02837500000004</v>
+        <v>630.73599999999999</v>
       </c>
       <c r="AC11" s="2">
         <f>+AC9-AC10</f>
-        <v>446.78507500000001</v>
+        <v>1048.8720000000001</v>
       </c>
       <c r="AD11" s="2">
         <f>+AD9-AD10</f>
-        <v>481.39834999999999</v>
-      </c>
-      <c r="AO11" s="2">
-        <f>+AO9-AO10</f>
+        <v>829.31000000000017</v>
+      </c>
+      <c r="AE11" s="2">
+        <f>+AE9-AE10</f>
+        <v>956.05299999999988</v>
+      </c>
+      <c r="AS11" s="2">
+        <f>+AS9-AS10</f>
         <v>805.30490999999984</v>
       </c>
-      <c r="AP11" s="2">
-        <f t="shared" ref="AP11:AR11" si="13">+AP9-AP10</f>
+      <c r="AT11" s="2">
+        <f t="shared" ref="AT11:AW11" si="17">+AT9-AT10</f>
         <v>833.53123499999992</v>
       </c>
-      <c r="AQ11" s="2">
-        <f t="shared" si="13"/>
-        <v>909.89730645000009</v>
-      </c>
-      <c r="AR11" s="2">
-        <f t="shared" si="13"/>
-        <v>988.57776587749993</v>
-      </c>
-    </row>
-    <row r="12" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU11" s="2">
+        <f t="shared" si="17"/>
+        <v>1718.6130000000003</v>
+      </c>
+      <c r="AV11" s="2">
+        <f t="shared" si="17"/>
+        <v>3032.3860000000004</v>
+      </c>
+      <c r="AW11" s="2">
+        <f t="shared" si="17"/>
+        <v>4704.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>38</v>
       </c>
@@ -2465,6 +2755,9 @@
       <c r="T12" s="2">
         <v>248.52600000000001</v>
       </c>
+      <c r="V12" s="2">
+        <v>272.14100000000002</v>
+      </c>
       <c r="W12" s="2">
         <v>260.995</v>
       </c>
@@ -2481,19 +2774,31 @@
         <v>265.12200000000001</v>
       </c>
       <c r="AB12" s="2">
-        <f t="shared" ref="AB12:AB13" si="14">+X12</f>
-        <v>294.142</v>
+        <v>323.62099999999998</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" ref="AC12:AC13" si="15">+Y12</f>
-        <v>270.92599999999999</v>
+        <v>358.81400000000002</v>
       </c>
       <c r="AD12" s="2">
-        <f t="shared" ref="AD12:AD13" si="16">+Z12</f>
-        <v>300.16899999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>372.21800000000002</v>
+      </c>
+      <c r="AE12" s="2">
+        <v>364.86599999999999</v>
+      </c>
+      <c r="AU12" s="2">
+        <f>SUM(W12:Z12)</f>
+        <v>1126.232</v>
+      </c>
+      <c r="AV12" s="2">
+        <f>SUM(AA12:AD12)</f>
+        <v>1319.7750000000001</v>
+      </c>
+      <c r="AW12" s="2">
+        <f>SUM(AE12:AH12)</f>
+        <v>364.86599999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>39</v>
       </c>
@@ -2540,6 +2845,9 @@
       <c r="T13" s="2">
         <v>214.68899999999999</v>
       </c>
+      <c r="V13" s="2">
+        <v>198.12299999999999</v>
+      </c>
       <c r="W13" s="2">
         <v>210.797</v>
       </c>
@@ -2556,19 +2864,31 @@
         <v>239.94900000000001</v>
       </c>
       <c r="AB13" s="2">
-        <f>+X13</f>
-        <v>248.39699999999999</v>
+        <v>323.31400000000002</v>
       </c>
       <c r="AC13" s="2">
-        <f t="shared" si="15"/>
-        <v>220.99299999999999</v>
+        <v>322.07600000000002</v>
       </c>
       <c r="AD13" s="2">
-        <f t="shared" si="16"/>
-        <v>295.339</v>
-      </c>
-    </row>
-    <row r="14" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>325.37400000000002</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>322.55099999999999</v>
+      </c>
+      <c r="AU13" s="2">
+        <f>SUM(W13:Z13)</f>
+        <v>975.52599999999984</v>
+      </c>
+      <c r="AV13" s="2">
+        <f>SUM(AA13:AD13)</f>
+        <v>1210.7130000000002</v>
+      </c>
+      <c r="AW13" s="2">
+        <f>SUM(AE13:AH13)</f>
+        <v>322.55099999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
@@ -2579,119 +2899,126 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
       <c r="I14" s="16">
-        <f t="shared" ref="I14:R14" si="17">+I12+I13</f>
+        <f t="shared" ref="I14:R14" si="18">+I12+I13</f>
         <v>329.255</v>
       </c>
       <c r="J14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>334.76</v>
       </c>
       <c r="K14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>332.75800000000004</v>
       </c>
       <c r="L14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>327.95799999999997</v>
       </c>
       <c r="M14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>336.64699999999999</v>
       </c>
       <c r="N14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>415.43200000000002</v>
       </c>
       <c r="O14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>324.36400000000003</v>
       </c>
       <c r="P14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>375.69600000000003</v>
       </c>
       <c r="Q14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>481.23</v>
       </c>
       <c r="R14" s="16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>235.85900000000001</v>
       </c>
       <c r="S14" s="16">
-        <f t="shared" ref="S14:X14" si="18">+S12+S13</f>
+        <f t="shared" ref="S14:X14" si="19">+S12+S13</f>
         <v>183.65899999999999</v>
       </c>
       <c r="T14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>463.21500000000003</v>
       </c>
       <c r="U14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="V14" s="16">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="19"/>
+        <v>470.26400000000001</v>
       </c>
       <c r="W14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>471.79200000000003</v>
       </c>
       <c r="X14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>542.53899999999999</v>
       </c>
       <c r="Y14" s="16">
-        <f t="shared" ref="Y14:AA14" si="19">+Y12+Y13</f>
+        <f t="shared" ref="Y14:AA14" si="20">+Y12+Y13</f>
         <v>491.91899999999998</v>
       </c>
       <c r="Z14" s="16">
-        <f t="shared" si="19"/>
-        <v>595.50800000000004</v>
-      </c>
-      <c r="AA14" s="16">
-        <f t="shared" si="19"/>
-        <v>505.07100000000003</v>
-      </c>
-      <c r="AB14" s="16">
-        <f t="shared" ref="AB14:AD14" si="20">+AB12+AB13</f>
-        <v>542.53899999999999</v>
-      </c>
-      <c r="AC14" s="16">
-        <f t="shared" si="20"/>
-        <v>491.91899999999998</v>
-      </c>
-      <c r="AD14" s="16">
         <f t="shared" si="20"/>
         <v>595.50800000000004</v>
       </c>
-      <c r="AN14" s="16">
-        <f t="shared" ref="AN14:AS14" si="21">+AN12+AN13</f>
+      <c r="AA14" s="16">
+        <f t="shared" si="20"/>
+        <v>505.07100000000003</v>
+      </c>
+      <c r="AB14" s="16">
+        <f t="shared" ref="AB14:AE14" si="21">+AB12+AB13</f>
+        <v>646.93499999999995</v>
+      </c>
+      <c r="AC14" s="16">
+        <f t="shared" si="21"/>
+        <v>680.8900000000001</v>
+      </c>
+      <c r="AD14" s="16">
+        <f t="shared" si="21"/>
+        <v>697.5920000000001</v>
+      </c>
+      <c r="AE14" s="16">
+        <f t="shared" si="21"/>
+        <v>687.41699999999992</v>
+      </c>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="16"/>
+      <c r="AR14" s="16">
+        <f t="shared" ref="AR14:AW14" si="22">+AR12+AR13</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="16">
-        <f t="shared" si="21"/>
+      <c r="AS14" s="16">
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AP14" s="16">
-        <f t="shared" si="21"/>
+      <c r="AT14" s="16">
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AQ14" s="16">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AR14" s="16">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AS14" s="16">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU14" s="16">
+        <f t="shared" si="22"/>
+        <v>2101.7579999999998</v>
+      </c>
+      <c r="AV14" s="16">
+        <f t="shared" si="22"/>
+        <v>2530.4880000000003</v>
+      </c>
+      <c r="AW14" s="16">
+        <f t="shared" si="22"/>
+        <v>687.41699999999992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
@@ -2702,119 +3029,126 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
       <c r="I15" s="16">
-        <f t="shared" ref="I15:R15" si="22">+I11-I14</f>
+        <f t="shared" ref="I15:R15" si="23">+I11-I14</f>
         <v>-225.19899999999998</v>
       </c>
       <c r="J15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-194.22200000000001</v>
       </c>
       <c r="K15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-186.25400000000002</v>
       </c>
       <c r="L15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-146.15999999999997</v>
       </c>
       <c r="M15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-181.67700000000002</v>
       </c>
       <c r="N15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-194.56099999999998</v>
       </c>
       <c r="O15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-146.73200000000003</v>
       </c>
       <c r="P15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-191.68600000000001</v>
       </c>
       <c r="Q15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-253.43100000000004</v>
       </c>
       <c r="R15" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-19.995090000000033</v>
       </c>
       <c r="S15" s="16">
-        <f t="shared" ref="S15:X15" si="23">+S11-S14</f>
+        <f t="shared" ref="S15:X15" si="24">+S11-S14</f>
         <v>80.761999999999944</v>
       </c>
       <c r="T15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-229.83100000000007</v>
       </c>
       <c r="U15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>313.15300000000002</v>
       </c>
       <c r="V15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
+        <v>-116.404</v>
+      </c>
+      <c r="W15" s="16">
+        <f t="shared" si="24"/>
+        <v>-43.435000000000002</v>
+      </c>
+      <c r="X15" s="16">
+        <f t="shared" si="24"/>
+        <v>-158.81499999999994</v>
+      </c>
+      <c r="Y15" s="16">
+        <f t="shared" ref="Y15:AA15" si="25">+Y11-Y14</f>
+        <v>-76.904999999999973</v>
+      </c>
+      <c r="Z15" s="16">
+        <f t="shared" si="25"/>
+        <v>-103.99000000000001</v>
+      </c>
+      <c r="AA15" s="16">
+        <f t="shared" si="25"/>
+        <v>18.396999999999935</v>
+      </c>
+      <c r="AB15" s="16">
+        <f t="shared" ref="AB15:AE15" si="26">+AB11-AB14</f>
+        <v>-16.198999999999955</v>
+      </c>
+      <c r="AC15" s="16">
+        <f t="shared" si="26"/>
+        <v>367.98199999999997</v>
+      </c>
+      <c r="AD15" s="16">
+        <f t="shared" si="26"/>
+        <v>131.71800000000007</v>
+      </c>
+      <c r="AE15" s="16">
+        <f t="shared" si="26"/>
+        <v>268.63599999999997</v>
+      </c>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="16"/>
+      <c r="AR15" s="16">
+        <f t="shared" ref="AR15:AW15" si="27">+AR11-AR14</f>
         <v>0</v>
       </c>
-      <c r="W15" s="16">
-        <f t="shared" si="23"/>
-        <v>-43.435000000000002</v>
-      </c>
-      <c r="X15" s="16">
-        <f t="shared" si="23"/>
-        <v>-158.81499999999994</v>
-      </c>
-      <c r="Y15" s="16">
-        <f t="shared" ref="Y15:AA15" si="24">+Y11-Y14</f>
-        <v>-76.904999999999973</v>
-      </c>
-      <c r="Z15" s="16">
-        <f t="shared" si="24"/>
-        <v>-103.99000000000001</v>
-      </c>
-      <c r="AA15" s="16">
-        <f t="shared" si="24"/>
-        <v>18.396999999999935</v>
-      </c>
-      <c r="AB15" s="16">
-        <f t="shared" ref="AB15:AD15" si="25">+AB11-AB14</f>
-        <v>-138.51062499999995</v>
-      </c>
-      <c r="AC15" s="16">
-        <f t="shared" si="25"/>
-        <v>-45.133924999999977</v>
-      </c>
-      <c r="AD15" s="16">
-        <f t="shared" si="25"/>
-        <v>-114.10965000000004</v>
-      </c>
-      <c r="AN15" s="16">
-        <f t="shared" ref="AN15:AS15" si="26">+AN11-AN14</f>
-        <v>0</v>
-      </c>
-      <c r="AO15" s="16">
-        <f t="shared" si="26"/>
+      <c r="AS15" s="16">
+        <f t="shared" si="27"/>
         <v>805.30490999999984</v>
       </c>
-      <c r="AP15" s="16">
-        <f t="shared" si="26"/>
+      <c r="AT15" s="16">
+        <f t="shared" si="27"/>
         <v>833.53123499999992</v>
       </c>
-      <c r="AQ15" s="16">
-        <f t="shared" si="26"/>
-        <v>909.89730645000009</v>
-      </c>
-      <c r="AR15" s="16">
-        <f t="shared" si="26"/>
-        <v>988.57776587749993</v>
-      </c>
-      <c r="AS15" s="16">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AU15" s="16">
+        <f t="shared" si="27"/>
+        <v>-383.14499999999953</v>
+      </c>
+      <c r="AV15" s="16">
+        <f t="shared" si="27"/>
+        <v>501.89800000000014</v>
+      </c>
+      <c r="AW15" s="16">
+        <f t="shared" si="27"/>
+        <v>4016.7829999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>47</v>
       </c>
@@ -2865,6 +3199,10 @@
         <f>-30.035+21.075-35.418</f>
         <v>-44.378</v>
       </c>
+      <c r="V16" s="2">
+        <f>-31.338+30.406</f>
+        <v>-0.93200000000000216</v>
+      </c>
       <c r="X16" s="2">
         <f>-33.258+29.182-55.705</f>
         <v>-59.781000000000006</v>
@@ -2882,16 +3220,35 @@
         <v>-59.673000000000002</v>
       </c>
       <c r="AB16" s="2">
-        <v>0</v>
+        <f>-40.246+27.486</f>
+        <v>-12.760000000000002</v>
       </c>
       <c r="AC16" s="2">
-        <v>0</v>
+        <f>-44.398+28.681</f>
+        <v>-15.717000000000002</v>
       </c>
       <c r="AD16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f>-65.4+26.63</f>
+        <v>-38.77000000000001</v>
+      </c>
+      <c r="AE16" s="2">
+        <f>-69.286+26.598</f>
+        <v>-42.688000000000002</v>
+      </c>
+      <c r="AU16" s="2">
+        <f>SUM(W16:Z16)</f>
+        <v>-69.962999999999994</v>
+      </c>
+      <c r="AV16" s="2">
+        <f>SUM(AA16:AD16)</f>
+        <v>-126.92000000000002</v>
+      </c>
+      <c r="AW16" s="2">
+        <f>SUM(AE16:AH16)</f>
+        <v>-42.688000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="2:49" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
@@ -2902,95 +3259,114 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
       <c r="I17" s="16">
-        <f t="shared" ref="I17:AD17" si="27">+I15+I16</f>
+        <f t="shared" ref="I17:AE17" si="28">+I15+I16</f>
         <v>-252.44899999999998</v>
       </c>
       <c r="J17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-243.59900000000002</v>
       </c>
       <c r="K17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-199.27500000000001</v>
       </c>
       <c r="L17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-188.33099999999996</v>
       </c>
       <c r="M17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-204.23600000000002</v>
       </c>
       <c r="N17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-260.30200000000002</v>
       </c>
       <c r="O17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-239.35600000000002</v>
       </c>
       <c r="P17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-274.673</v>
       </c>
       <c r="Q17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-324.74800000000005</v>
       </c>
       <c r="R17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-19.995090000000033</v>
       </c>
       <c r="S17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>80.761999999999944</v>
       </c>
       <c r="T17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-274.20900000000006</v>
       </c>
       <c r="U17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>313.15300000000002</v>
       </c>
       <c r="V17" s="16">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>-117.336</v>
       </c>
       <c r="W17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-43.435000000000002</v>
       </c>
       <c r="X17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-218.59599999999995</v>
       </c>
       <c r="Y17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-79.134999999999962</v>
       </c>
       <c r="Z17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-111.94200000000001</v>
       </c>
       <c r="AA17" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-41.276000000000067</v>
       </c>
       <c r="AB17" s="16">
-        <f t="shared" si="27"/>
-        <v>-138.51062499999995</v>
+        <f t="shared" si="28"/>
+        <v>-28.958999999999957</v>
       </c>
       <c r="AC17" s="16">
-        <f t="shared" si="27"/>
-        <v>-45.133924999999977</v>
+        <f t="shared" si="28"/>
+        <v>352.26499999999999</v>
       </c>
       <c r="AD17" s="16">
-        <f t="shared" si="27"/>
-        <v>-114.10965000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="28"/>
+        <v>92.948000000000064</v>
+      </c>
+      <c r="AE17" s="16">
+        <f t="shared" si="28"/>
+        <v>225.94799999999998</v>
+      </c>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AU17" s="2">
+        <f>+AU15+AU16</f>
+        <v>-453.10799999999949</v>
+      </c>
+      <c r="AV17" s="2">
+        <f>+AV15+AV16</f>
+        <v>374.97800000000012</v>
+      </c>
+      <c r="AW17" s="2">
+        <f>+AW15+AW16</f>
+        <v>3974.0949999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="2:49" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>45</v>
       </c>
@@ -3031,6 +3407,9 @@
       <c r="T18" s="2">
         <v>1.8149999999999999</v>
       </c>
+      <c r="V18" s="2">
+        <v>0</v>
+      </c>
       <c r="X18" s="2">
         <v>5.7220000000000004</v>
       </c>
@@ -3044,19 +3423,31 @@
         <v>0</v>
       </c>
       <c r="AB18" s="2">
-        <f>+AB17*0.15</f>
-        <v>-20.776593749999993</v>
+        <v>0</v>
       </c>
       <c r="AC18" s="2">
-        <f>+AC17*0.15</f>
-        <v>-6.7700887499999967</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="2">
-        <f>+AD17*0.15</f>
-        <v>-17.116447500000007</v>
-      </c>
-    </row>
-    <row r="19" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="2">
+        <v>15.662000000000001</v>
+      </c>
+      <c r="AU18" s="2">
+        <f>SUM(W18:Z18)</f>
+        <v>5.7220000000000004</v>
+      </c>
+      <c r="AV18" s="2">
+        <f>SUM(AA18:AD18)</f>
+        <v>0</v>
+      </c>
+      <c r="AW18" s="2">
+        <f>SUM(AE18:AH18)</f>
+        <v>15.662000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:49" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
@@ -3067,47 +3458,47 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
       <c r="I19" s="16">
-        <f t="shared" ref="I19:S19" si="28">+I17-I18</f>
+        <f t="shared" ref="I19:S19" si="29">+I17-I18</f>
         <v>-253.28799999999998</v>
       </c>
       <c r="J19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-243.54000000000002</v>
       </c>
       <c r="K19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-200.291</v>
       </c>
       <c r="L19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-187.10299999999995</v>
       </c>
       <c r="M19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-204.51400000000001</v>
       </c>
       <c r="N19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-258.46000000000004</v>
       </c>
       <c r="O19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-240.34100000000004</v>
       </c>
       <c r="P19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-277.40199999999999</v>
       </c>
       <c r="Q19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-324.74800000000005</v>
       </c>
       <c r="R19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-19.995090000000033</v>
       </c>
       <c r="S19" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>80.761999999999944</v>
       </c>
       <c r="T19" s="2">
@@ -3120,7 +3511,7 @@
       </c>
       <c r="V19" s="2">
         <f>+V17-V18</f>
-        <v>0</v>
+        <v>-117.336</v>
       </c>
       <c r="W19" s="2">
         <f>+W17-W18</f>
@@ -3131,31 +3522,47 @@
         <v>-224.31799999999996</v>
       </c>
       <c r="Y19" s="2">
-        <f t="shared" ref="Y19:AD19" si="29">+Y17-Y18</f>
+        <f t="shared" ref="Y19:AE19" si="30">+Y17-Y18</f>
         <v>-79.134999999999962</v>
       </c>
       <c r="Z19" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-111.94200000000001</v>
       </c>
       <c r="AA19" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-41.276000000000067</v>
       </c>
       <c r="AB19" s="2">
-        <f t="shared" si="29"/>
-        <v>-117.73403124999996</v>
+        <f t="shared" si="30"/>
+        <v>-28.958999999999957</v>
       </c>
       <c r="AC19" s="2">
-        <f t="shared" si="29"/>
-        <v>-38.363836249999977</v>
+        <f t="shared" si="30"/>
+        <v>352.26499999999999</v>
       </c>
       <c r="AD19" s="2">
-        <f t="shared" si="29"/>
-        <v>-96.993202500000038</v>
-      </c>
-    </row>
-    <row r="20" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="30"/>
+        <v>92.948000000000064</v>
+      </c>
+      <c r="AE19" s="2">
+        <f t="shared" si="30"/>
+        <v>210.28599999999997</v>
+      </c>
+      <c r="AU19" s="2">
+        <f>+AU17-AU18</f>
+        <v>-458.82999999999947</v>
+      </c>
+      <c r="AV19" s="2">
+        <f>+AV17-AV18</f>
+        <v>374.97800000000012</v>
+      </c>
+      <c r="AW19" s="2">
+        <f>+AW17-AW18</f>
+        <v>3958.433</v>
+      </c>
+    </row>
+    <row r="20" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>43</v>
       </c>
@@ -3166,56 +3573,60 @@
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15">
-        <f t="shared" ref="I20:T20" si="30">+I19/I21</f>
+        <f t="shared" ref="I20:T20" si="31">+I19/I21</f>
         <v>-2.1837808011311708</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2.094535321740028</v>
       </c>
       <c r="K20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1.710719166381961</v>
       </c>
       <c r="L20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1.5886883130115812</v>
       </c>
       <c r="M20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1.7165711216122075</v>
       </c>
       <c r="N20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2.1579153899459813</v>
       </c>
       <c r="O20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1.9963037718139762</v>
       </c>
       <c r="P20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2.2945506881948119</v>
       </c>
       <c r="Q20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2.6582518867770086</v>
       </c>
       <c r="R20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-0.16367147978979449</v>
       </c>
       <c r="S20" s="15"/>
       <c r="T20" s="15">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-2.2142324260582873</v>
       </c>
+      <c r="V20" s="15">
+        <f t="shared" ref="V20:Y20" si="32">+V19/V21</f>
+        <v>-0.93410713859234318</v>
+      </c>
       <c r="X20" s="15">
-        <f t="shared" ref="X20:Y20" si="31">+X19/X21</f>
+        <f t="shared" si="32"/>
         <v>-1.7700046554567472</v>
       </c>
       <c r="Y20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-0.61540555253130069</v>
       </c>
       <c r="Z20" s="1">
@@ -3228,18 +3639,34 @@
       </c>
       <c r="AB20" s="1">
         <f>+AB19/AB21</f>
-        <v>-0.90790918327215497</v>
+        <v>-0.22169060232109472</v>
       </c>
       <c r="AC20" s="1">
-        <f t="shared" ref="AC20:AE20" si="32">+AC19/AC21</f>
-        <v>-0.29584376638699511</v>
+        <f t="shared" ref="AC20:AE20" si="33">+AC19/AC21</f>
+        <v>2.5647625010921162</v>
       </c>
       <c r="AD20" s="1">
-        <f t="shared" si="32"/>
-        <v>-0.74796571840587345</v>
-      </c>
-    </row>
-    <row r="21" spans="2:45" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="33"/>
+        <v>0.68203197804536264</v>
+      </c>
+      <c r="AE20" s="1">
+        <f t="shared" si="33"/>
+        <v>1.5430324109743836</v>
+      </c>
+      <c r="AU20" s="1">
+        <f>+AU19/AU21</f>
+        <v>-3.5805160246489001</v>
+      </c>
+      <c r="AV20" s="1">
+        <f>+AV19/AV21</f>
+        <v>2.8091764322489912</v>
+      </c>
+      <c r="AW20" s="1">
+        <f>+AW19/AW21</f>
+        <v>29.046110609696139</v>
+      </c>
+    </row>
+    <row r="21" spans="2:49" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>42</v>
       </c>
@@ -3283,6 +3710,9 @@
       <c r="T21" s="2">
         <v>124.65900000000001</v>
       </c>
+      <c r="V21" s="2">
+        <v>125.613</v>
+      </c>
       <c r="X21" s="2">
         <v>126.733</v>
       </c>
@@ -3296,19 +3726,32 @@
         <v>129.67599999999999</v>
       </c>
       <c r="AB21" s="2">
-        <f>+AA21</f>
-        <v>129.67599999999999</v>
+        <v>130.62799999999999</v>
       </c>
       <c r="AC21" s="2">
-        <f t="shared" ref="AC21:AE21" si="33">+AB21</f>
-        <v>129.67599999999999</v>
+        <v>137.34800000000001</v>
       </c>
       <c r="AD21" s="2">
-        <f t="shared" si="33"/>
-        <v>129.67599999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="2:45" s="13" customFormat="1" x14ac:dyDescent="0.2">
+        <v>136.28100000000001</v>
+      </c>
+      <c r="AE21" s="2">
+        <f>+AD21</f>
+        <v>136.28100000000001</v>
+      </c>
+      <c r="AU21" s="2">
+        <f>AVERAGE(W21:Z21)</f>
+        <v>128.14633333333333</v>
+      </c>
+      <c r="AV21" s="2">
+        <f>AVERAGE(AA21:AD21)</f>
+        <v>133.48325</v>
+      </c>
+      <c r="AW21" s="2">
+        <f>AVERAGE(AE21:AH21)</f>
+        <v>136.28100000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:49" s="13" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B23" s="17" t="s">
         <v>59</v>
       </c>
@@ -3360,7 +3803,7 @@
       </c>
       <c r="V23" s="20">
         <f t="shared" si="35"/>
-        <v>-1</v>
+        <v>0.69072236299249856</v>
       </c>
       <c r="W23" s="20">
         <f t="shared" si="35"/>
@@ -3374,9 +3817,9 @@
         <f t="shared" si="35"/>
         <v>0.59959827943529187</v>
       </c>
-      <c r="Z23" s="20" t="e">
+      <c r="Z23" s="20">
         <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
+        <v>0.3516276340745661</v>
       </c>
       <c r="AA23" s="20">
         <f t="shared" ref="AA23" si="36">+AA9/W9-1</f>
@@ -3384,30 +3827,50 @@
       </c>
       <c r="AB23" s="20">
         <f t="shared" ref="AB23" si="37">+AB9/X9-1</f>
-        <v>5.0688998134377883E-2</v>
+        <v>0.71020300798415525</v>
       </c>
       <c r="AC23" s="20">
         <f t="shared" ref="AC23" si="38">+AC9/Y9-1</f>
-        <v>4.93303308518942E-2</v>
+        <v>1.4934690039707021</v>
       </c>
       <c r="AD23" s="20">
-        <f t="shared" ref="AD23" si="39">+AD9/Z9-1</f>
-        <v>-4.7084556689409252E-2</v>
-      </c>
-      <c r="AP23" s="26">
-        <f>+AP9/AO9-1</f>
+        <f t="shared" ref="AD23:AH23" si="39">+AD9/Z9-1</f>
+        <v>0.84581591190153715</v>
+      </c>
+      <c r="AE23" s="20">
+        <f t="shared" si="39"/>
+        <v>0.96609624173125286</v>
+      </c>
+      <c r="AF23" s="20">
+        <f t="shared" si="39"/>
+        <v>0.5362891290945071</v>
+      </c>
+      <c r="AG23" s="20">
+        <f t="shared" si="39"/>
+        <v>-4.9734753319786718E-3</v>
+      </c>
+      <c r="AH23" s="20">
+        <f t="shared" si="39"/>
+        <v>0.20025833315861963</v>
+      </c>
+      <c r="AT23" s="26">
+        <f>+AT9/AS9-1</f>
         <v>4.3424661804126963E-2</v>
       </c>
-      <c r="AQ23" s="26">
-        <f>+AQ9/AP9-1</f>
-        <v>9.161752822616176E-2</v>
-      </c>
-      <c r="AR23" s="26">
-        <f>+AR9/AQ9-1</f>
-        <v>8.6471801674493198E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AU23" s="26">
+        <f>+AU9/AT9-1</f>
+        <v>1.0333321882052808</v>
+      </c>
+      <c r="AV23" s="26">
+        <f>+AV9/AU9-1</f>
+        <v>0.81852591329114888</v>
+      </c>
+      <c r="AW23" s="26">
+        <f>+AW9/AV9-1</f>
+        <v>0.3236719242936188</v>
+      </c>
+    </row>
+    <row r="24" spans="2:49" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>60</v>
       </c>
@@ -3463,9 +3926,9 @@
         <f t="shared" si="40"/>
         <v>1</v>
       </c>
-      <c r="V24" s="19" t="e">
+      <c r="V24" s="19">
         <f t="shared" si="40"/>
-        <v>#DIV/0!</v>
+        <v>0.80474303985736317</v>
       </c>
       <c r="W24" s="19">
         <f t="shared" si="40"/>
@@ -3484,38 +3947,57 @@
         <v>0.82700497194343259</v>
       </c>
       <c r="AA24" s="19">
-        <f t="shared" ref="AA24:AD24" si="41">+AA11/AA9</f>
+        <f t="shared" ref="AA24:AH24" si="41">+AA11/AA9</f>
         <v>0.8817773405586784</v>
       </c>
       <c r="AB24" s="19">
         <f t="shared" si="41"/>
-        <v>0.85</v>
+        <v>0.81523196012868226</v>
       </c>
       <c r="AC24" s="19">
         <f t="shared" si="41"/>
-        <v>0.85</v>
+        <v>0.83975193470752407</v>
       </c>
       <c r="AD24" s="19">
         <f t="shared" si="41"/>
-        <v>0.85</v>
-      </c>
-      <c r="AO24" s="19">
-        <f t="shared" ref="AO24:AR24" si="42">+AO11/AO9</f>
+        <v>0.75595720456905136</v>
+      </c>
+      <c r="AE24" s="19">
+        <f t="shared" si="41"/>
+        <v>0.8191170989783022</v>
+      </c>
+      <c r="AF24" s="19">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="19">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="19">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AS24" s="19">
+        <f t="shared" ref="AS24:AW24" si="42">+AS11/AS9</f>
         <v>0.83671519855370602</v>
       </c>
-      <c r="AP24" s="19">
+      <c r="AT24" s="19">
         <f t="shared" si="42"/>
         <v>0.83</v>
       </c>
-      <c r="AQ24" s="19">
+      <c r="AU24" s="19">
         <f t="shared" si="42"/>
-        <v>0.83000000000000007</v>
-      </c>
-      <c r="AR24" s="19">
+        <v>0.84163923010132802</v>
+      </c>
+      <c r="AV24" s="19">
         <f t="shared" si="42"/>
-        <v>0.83</v>
-      </c>
-      <c r="AS24" s="19"/>
+        <v>0.81660656449791691</v>
+      </c>
+      <c r="AW24" s="19">
+        <f t="shared" si="42"/>
+        <v>0.95704818524605295</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3531,77 +4013,77 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C88543-0125-48E2-917E-AFC096EB64C2}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="C7" s="22" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C9" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D10" t="s">
+    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C13" s="22" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C13" s="22" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -3616,18 +4098,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366D0B77-8D3D-4AA1-AC03-6C0EAC385E3F}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>62</v>
       </c>
@@ -3635,7 +4117,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>63</v>
       </c>
@@ -3643,7 +4125,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -3651,7 +4133,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
@@ -3659,12 +4141,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C7" s="22" t="s">
         <v>101</v>
       </c>
@@ -3680,18 +4162,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4112C7B2-025D-4CC8-B8DF-D63413D3CD25}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>62</v>
       </c>
@@ -3699,7 +4181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>63</v>
       </c>
@@ -3707,7 +4189,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -3715,39 +4197,39 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C6" s="22" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3761,18 +4243,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F5F252-D1FE-41F6-93EB-75B65F0EBF79}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>62</v>
       </c>
@@ -3780,7 +4262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>63</v>
       </c>
@@ -3788,7 +4270,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -3796,7 +4278,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -3804,7 +4286,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>69</v>
       </c>
@@ -3812,32 +4294,32 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C8" s="22" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C12" s="22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C14" s="22" t="s">
         <v>73</v>
       </c>

--- a/ALNY.xlsx
+++ b/ALNY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE91D83B-9929-4494-BDE1-E21032EA4AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EE2A82-3AA5-493B-B06F-B7DD0F0D9D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14690" yWindow="2940" windowWidth="22360" windowHeight="16580" xr2:uid="{7C34F31A-DE2D-4EBA-93CC-6997970EE8B3}"/>
+    <workbookView xWindow="16250" yWindow="2920" windowWidth="19050" windowHeight="16100" activeTab="1" xr2:uid="{7C34F31A-DE2D-4EBA-93CC-6997970EE8B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -664,7 +664,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -708,7 +708,6 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1180,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>382</v>
+        <v>272.29000000000002</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -1220,7 +1219,7 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>51001.802885999998</v>
+        <v>36354.138502170004</v>
       </c>
       <c r="M4" s="3"/>
     </row>
@@ -1300,7 +1299,7 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>49001.951886000003</v>
+        <v>34354.287502170009</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -1321,7 +1320,7 @@
       <c r="C9" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" t="s">
         <v>151</v>
       </c>
       <c r="H9" s="5"/>
@@ -1767,16 +1766,15 @@
         <v>20.481000000000002</v>
       </c>
       <c r="AF3" s="2">
-        <f>+AE3-1</f>
-        <v>19.481000000000002</v>
+        <v>18.460999999999999</v>
       </c>
       <c r="AG3" s="2">
         <f>+AF3-1</f>
-        <v>18.481000000000002</v>
+        <v>17.460999999999999</v>
       </c>
       <c r="AH3" s="2">
         <f>+AG3-1</f>
-        <v>17.481000000000002</v>
+        <v>16.460999999999999</v>
       </c>
       <c r="AS3" s="2">
         <f t="shared" ref="AS3:AS8" si="1">SUM(O3:R3)</f>
@@ -1787,16 +1785,16 @@
         <v>464.26960000000003</v>
       </c>
       <c r="AU3" s="2">
-        <f>SUM(W3:Z3)</f>
+        <f t="shared" ref="AU3:AU8" si="2">SUM(W3:Z3)</f>
         <v>252.75400000000002</v>
       </c>
       <c r="AV3" s="2">
-        <f>SUM(AA3:AD3)</f>
+        <f t="shared" ref="AV3:AV8" si="3">SUM(AA3:AD3)</f>
         <v>172.3</v>
       </c>
       <c r="AW3" s="2">
-        <f>SUM(AE3:AH3)</f>
-        <v>75.924000000000007</v>
+        <f t="shared" ref="AW3:AW8" si="4">SUM(AE3:AH3)</f>
+        <v>72.864000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1863,16 +1861,15 @@
         <v>889.93100000000004</v>
       </c>
       <c r="AF4" s="2">
-        <f>+AE4+50</f>
-        <v>939.93100000000004</v>
+        <v>1011.7619999999999</v>
       </c>
       <c r="AG4" s="2">
         <f>+AF4+50</f>
-        <v>989.93100000000004</v>
+        <v>1061.7619999999999</v>
       </c>
       <c r="AH4" s="2">
         <f>+AG4+50</f>
-        <v>1039.931</v>
+        <v>1111.7619999999999</v>
       </c>
       <c r="AS4" s="2">
         <f t="shared" si="1"/>
@@ -1882,16 +1879,16 @@
         <v>200</v>
       </c>
       <c r="AU4" s="2">
-        <f>SUM(W4:Z4)</f>
+        <f t="shared" si="2"/>
         <v>970.94</v>
       </c>
       <c r="AV4" s="2">
-        <f>SUM(AA4:AD4)</f>
+        <f t="shared" si="3"/>
         <v>2313.8440000000001</v>
       </c>
       <c r="AW4" s="2">
-        <f>SUM(AE4:AH4)</f>
-        <v>3859.7240000000002</v>
+        <f t="shared" si="4"/>
+        <v>4075.2169999999996</v>
       </c>
     </row>
     <row r="5" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1975,15 +1972,14 @@
         <v>74.394000000000005</v>
       </c>
       <c r="AF5" s="2">
-        <f>+AB5</f>
-        <v>80.849000000000004</v>
+        <v>89.763999999999996</v>
       </c>
       <c r="AG5" s="2">
-        <f t="shared" ref="AG5:AG7" si="2">+AC5</f>
+        <f t="shared" ref="AG5:AG6" si="5">+AC5</f>
         <v>73.873999999999995</v>
       </c>
       <c r="AH5" s="2">
-        <f t="shared" ref="AH5:AH7" si="3">+AD5</f>
+        <f t="shared" ref="AH5:AH6" si="6">+AD5</f>
         <v>86.796000000000006</v>
       </c>
       <c r="AS5" s="2">
@@ -1991,20 +1987,20 @@
         <v>175.74499999999998</v>
       </c>
       <c r="AT5" s="2">
-        <f t="shared" ref="AT5:AV6" si="4">+AS5*1.15</f>
+        <f t="shared" ref="AT5:AT6" si="7">+AS5*1.15</f>
         <v>202.10674999999995</v>
       </c>
       <c r="AU5" s="2">
-        <f>SUM(W5:Z5)</f>
+        <f t="shared" si="2"/>
         <v>256.226</v>
       </c>
       <c r="AV5" s="2">
-        <f>SUM(AA5:AD5)</f>
+        <f t="shared" si="3"/>
         <v>308.51900000000001</v>
       </c>
       <c r="AW5" s="2">
-        <f>SUM(AE5:AH5)</f>
-        <v>315.91300000000001</v>
+        <f t="shared" si="4"/>
+        <v>324.82800000000003</v>
       </c>
     </row>
     <row r="6" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2088,15 +2084,14 @@
         <v>51.320999999999998</v>
       </c>
       <c r="AF6" s="2">
-        <f t="shared" ref="AF6:AF7" si="5">+AB6</f>
-        <v>46.872</v>
+        <v>52.122</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>52.83</v>
       </c>
       <c r="AH6" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>49.646000000000001</v>
       </c>
       <c r="AS6" s="2">
@@ -2104,20 +2099,20 @@
         <v>65.381</v>
       </c>
       <c r="AT6" s="2">
+        <f t="shared" si="7"/>
+        <v>75.188149999999993</v>
+      </c>
+      <c r="AU6" s="2">
+        <f t="shared" si="2"/>
+        <v>167.477</v>
+      </c>
+      <c r="AV6" s="2">
+        <f t="shared" si="3"/>
+        <v>191.34800000000001</v>
+      </c>
+      <c r="AW6" s="2">
         <f t="shared" si="4"/>
-        <v>75.188149999999993</v>
-      </c>
-      <c r="AU6" s="2">
-        <f>SUM(W6:Z6)</f>
-        <v>167.477</v>
-      </c>
-      <c r="AV6" s="2">
-        <f>SUM(AA6:AD6)</f>
-        <v>191.34800000000001</v>
-      </c>
-      <c r="AW6" s="2">
-        <f>SUM(AE6:AH6)</f>
-        <v>200.66899999999998</v>
+        <v>205.91899999999998</v>
       </c>
     </row>
     <row r="7" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2199,16 +2194,15 @@
         <v>82.075000000000003</v>
       </c>
       <c r="AF7" s="2">
-        <f t="shared" si="5"/>
-        <v>61.496000000000002</v>
+        <v>47.164999999999999</v>
       </c>
       <c r="AG7" s="2">
         <f>+AF7</f>
-        <v>61.496000000000002</v>
+        <v>47.164999999999999</v>
       </c>
       <c r="AH7" s="2">
         <f>+AG7</f>
-        <v>61.496000000000002</v>
+        <v>47.164999999999999</v>
       </c>
       <c r="AS7" s="2">
         <f t="shared" si="1"/>
@@ -2219,16 +2213,16 @@
         <v>46.281999999999996</v>
       </c>
       <c r="AU7" s="2">
-        <f>SUM(W7:Z7)</f>
+        <f t="shared" si="2"/>
         <v>302.79199999999997</v>
       </c>
       <c r="AV7" s="2">
-        <f>SUM(AA7:AD7)</f>
+        <f t="shared" si="3"/>
         <v>553.36599999999999</v>
       </c>
       <c r="AW7" s="2">
-        <f>SUM(AE7:AH7)</f>
-        <v>266.56299999999999</v>
+        <f t="shared" si="4"/>
+        <v>223.57</v>
       </c>
     </row>
     <row r="8" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2309,15 +2303,14 @@
         <v>48.972999999999999</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" ref="AF8" si="6">+AB8</f>
-        <v>39.981000000000002</v>
+        <v>71.674000000000007</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" ref="AG8" si="7">+AC8</f>
+        <f t="shared" ref="AG8" si="8">+AC8</f>
         <v>46.201999999999998</v>
       </c>
       <c r="AH8" s="2">
-        <f t="shared" ref="AH8" si="8">+AD8</f>
+        <f t="shared" ref="AH8" si="9">+AD8</f>
         <v>61.372999999999998</v>
       </c>
       <c r="AS8" s="2">
@@ -2329,16 +2322,16 @@
         <v>16.408000000000001</v>
       </c>
       <c r="AU8" s="2">
-        <f>SUM(W8:Z8)</f>
+        <f t="shared" si="2"/>
         <v>91.793999999999997</v>
       </c>
       <c r="AV8" s="2">
-        <f>SUM(AA8:AD8)</f>
+        <f t="shared" si="3"/>
         <v>174.02199999999999</v>
       </c>
       <c r="AW8" s="2">
-        <f>SUM(AE8:AH8)</f>
-        <v>196.529</v>
+        <f t="shared" si="4"/>
+        <v>228.22199999999998</v>
       </c>
     </row>
     <row r="9" spans="1:50" s="17" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -2352,108 +2345,108 @@
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18">
-        <f t="shared" ref="I9:P9" si="9">SUM(I3:I8)</f>
+        <f t="shared" ref="I9:P9" si="10">SUM(I3:I8)</f>
         <v>125.85300000000001</v>
       </c>
       <c r="J9" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>163.56199999999998</v>
       </c>
       <c r="K9" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>177.566</v>
       </c>
       <c r="L9" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>220.553</v>
       </c>
       <c r="M9" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>187.63299999999998</v>
       </c>
       <c r="N9" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>258.53500000000003</v>
       </c>
       <c r="O9" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>213.25900000000001</v>
       </c>
       <c r="P9" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>224.81800000000001</v>
       </c>
       <c r="Q9" s="18">
-        <f t="shared" ref="Q9:R9" si="10">SUM(Q3:Q8)</f>
+        <f t="shared" ref="Q9:R9" si="11">SUM(Q3:Q8)</f>
         <v>264.30599999999998</v>
       </c>
       <c r="R9" s="18">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>260.077</v>
       </c>
       <c r="S9" s="17">
-        <f t="shared" ref="S9:AA9" si="11">SUM(S3:S8)</f>
+        <f t="shared" ref="S9:AA9" si="12">SUM(S3:S8)</f>
         <v>319.28999999999996</v>
       </c>
       <c r="T9" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>318.75399999999996</v>
       </c>
       <c r="U9" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>313.15300000000002</v>
       </c>
       <c r="V9" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>439.71800000000002</v>
       </c>
       <c r="W9" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>494.33300000000003</v>
       </c>
       <c r="X9" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>452.39600000000002</v>
       </c>
       <c r="Y9" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>500.91899999999998</v>
       </c>
       <c r="Z9" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>594.33500000000004</v>
       </c>
       <c r="AA9" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>593.65099999999995</v>
       </c>
       <c r="AB9" s="17">
-        <f t="shared" ref="AB9" si="12">SUM(AB3:AB8)</f>
+        <f t="shared" ref="AB9" si="13">SUM(AB3:AB8)</f>
         <v>773.68899999999996</v>
       </c>
       <c r="AC9" s="17">
-        <f t="shared" ref="AC9" si="13">SUM(AC3:AC8)</f>
+        <f t="shared" ref="AC9" si="14">SUM(AC3:AC8)</f>
         <v>1249.0260000000001</v>
       </c>
       <c r="AD9" s="17">
-        <f t="shared" ref="AD9:AH9" si="14">SUM(AD3:AD8)</f>
+        <f t="shared" ref="AD9:AH9" si="15">SUM(AD3:AD8)</f>
         <v>1097.0330000000001</v>
       </c>
       <c r="AE9" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1167.175</v>
       </c>
       <c r="AF9" s="17">
-        <f t="shared" si="14"/>
-        <v>1188.6100000000001</v>
+        <f t="shared" si="15"/>
+        <v>1290.9479999999999</v>
       </c>
       <c r="AG9" s="17">
-        <f t="shared" si="14"/>
-        <v>1242.8140000000001</v>
+        <f t="shared" si="15"/>
+        <v>1299.2939999999999</v>
       </c>
       <c r="AH9" s="17">
-        <f t="shared" si="14"/>
-        <v>1316.7230000000002</v>
+        <f t="shared" si="15"/>
+        <v>1373.203</v>
       </c>
       <c r="AS9" s="17">
         <f>SUM(AS3:AS8)</f>
@@ -2473,7 +2466,7 @@
       </c>
       <c r="AW9" s="17">
         <f>SUM(AW3:AW8)</f>
-        <v>4915.3220000000001</v>
+        <v>5130.619999999999</v>
       </c>
     </row>
     <row r="10" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2570,6 +2563,18 @@
         <f>207.52+3.602</f>
         <v>211.12200000000001</v>
       </c>
+      <c r="AF10" s="2">
+        <f>298.261+0.19</f>
+        <v>298.45100000000002</v>
+      </c>
+      <c r="AG10" s="2">
+        <f>+AF10</f>
+        <v>298.45100000000002</v>
+      </c>
+      <c r="AH10" s="2">
+        <f>+AG10</f>
+        <v>298.45100000000002</v>
+      </c>
       <c r="AS10" s="2">
         <f>SUM(O10:R10)</f>
         <v>157.15509000000003</v>
@@ -2588,7 +2593,7 @@
       </c>
       <c r="AW10" s="2">
         <f>SUM(AE10:AH10)</f>
-        <v>211.12200000000001</v>
+        <v>1106.4750000000001</v>
       </c>
     </row>
     <row r="11" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2602,35 +2607,35 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16">
-        <f t="shared" ref="I11:P11" si="15">+I9-I10</f>
+        <f t="shared" ref="I11:P11" si="16">+I9-I10</f>
         <v>104.05600000000001</v>
       </c>
       <c r="J11" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>140.53799999999998</v>
       </c>
       <c r="K11" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>146.50400000000002</v>
       </c>
       <c r="L11" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>181.798</v>
       </c>
       <c r="M11" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>154.96999999999997</v>
       </c>
       <c r="N11" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>220.87100000000004</v>
       </c>
       <c r="O11" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>177.63200000000001</v>
       </c>
       <c r="P11" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>184.01000000000002</v>
       </c>
       <c r="Q11" s="16">
@@ -2642,39 +2647,39 @@
         <v>215.86390999999998</v>
       </c>
       <c r="S11" s="2">
-        <f t="shared" ref="S11:AA11" si="16">+S9-S10</f>
+        <f t="shared" ref="S11:AA11" si="17">+S9-S10</f>
         <v>264.42099999999994</v>
       </c>
       <c r="T11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>233.38399999999996</v>
       </c>
       <c r="U11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>313.15300000000002</v>
       </c>
       <c r="V11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>353.86</v>
       </c>
       <c r="W11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>428.35700000000003</v>
       </c>
       <c r="X11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>383.72400000000005</v>
       </c>
       <c r="Y11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>415.01400000000001</v>
       </c>
       <c r="Z11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>491.51800000000003</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>523.46799999999996</v>
       </c>
       <c r="AB11" s="2">
@@ -2693,25 +2698,37 @@
         <f>+AE9-AE10</f>
         <v>956.05299999999988</v>
       </c>
+      <c r="AF11" s="2">
+        <f>+AF9-AF10</f>
+        <v>992.49699999999984</v>
+      </c>
+      <c r="AG11" s="2">
+        <f>+AG9-AG10</f>
+        <v>1000.8429999999998</v>
+      </c>
+      <c r="AH11" s="2">
+        <f>+AH9-AH10</f>
+        <v>1074.752</v>
+      </c>
       <c r="AS11" s="2">
         <f>+AS9-AS10</f>
         <v>805.30490999999984</v>
       </c>
       <c r="AT11" s="2">
-        <f t="shared" ref="AT11:AW11" si="17">+AT9-AT10</f>
+        <f t="shared" ref="AT11:AW11" si="18">+AT9-AT10</f>
         <v>833.53123499999992</v>
       </c>
       <c r="AU11" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1718.6130000000003</v>
       </c>
       <c r="AV11" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>3032.3860000000004</v>
       </c>
       <c r="AW11" s="2">
-        <f t="shared" si="17"/>
-        <v>4704.2</v>
+        <f t="shared" si="18"/>
+        <v>4024.1449999999986</v>
       </c>
     </row>
     <row r="12" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2785,6 +2802,9 @@
       <c r="AE12" s="2">
         <v>364.86599999999999</v>
       </c>
+      <c r="AF12" s="2">
+        <v>377.24</v>
+      </c>
       <c r="AU12" s="2">
         <f>SUM(W12:Z12)</f>
         <v>1126.232</v>
@@ -2795,7 +2815,7 @@
       </c>
       <c r="AW12" s="2">
         <f>SUM(AE12:AH12)</f>
-        <v>364.86599999999999</v>
+        <v>742.10599999999999</v>
       </c>
     </row>
     <row r="13" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2875,6 +2895,9 @@
       <c r="AE13" s="2">
         <v>322.55099999999999</v>
       </c>
+      <c r="AF13" s="2">
+        <v>297.19099999999997</v>
+      </c>
       <c r="AU13" s="2">
         <f>SUM(W13:Z13)</f>
         <v>975.52599999999984</v>
@@ -2885,7 +2908,7 @@
       </c>
       <c r="AW13" s="2">
         <f>SUM(AE13:AH13)</f>
-        <v>322.55099999999999</v>
+        <v>619.74199999999996</v>
       </c>
     </row>
     <row r="14" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2899,123 +2922,132 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
       <c r="I14" s="16">
-        <f t="shared" ref="I14:R14" si="18">+I12+I13</f>
+        <f t="shared" ref="I14:R14" si="19">+I12+I13</f>
         <v>329.255</v>
       </c>
       <c r="J14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>334.76</v>
       </c>
       <c r="K14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>332.75800000000004</v>
       </c>
       <c r="L14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>327.95799999999997</v>
       </c>
       <c r="M14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>336.64699999999999</v>
       </c>
       <c r="N14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>415.43200000000002</v>
       </c>
       <c r="O14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>324.36400000000003</v>
       </c>
       <c r="P14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>375.69600000000003</v>
       </c>
       <c r="Q14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>481.23</v>
       </c>
       <c r="R14" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>235.85900000000001</v>
       </c>
       <c r="S14" s="16">
-        <f t="shared" ref="S14:X14" si="19">+S12+S13</f>
+        <f t="shared" ref="S14:X14" si="20">+S12+S13</f>
         <v>183.65899999999999</v>
       </c>
       <c r="T14" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>463.21500000000003</v>
       </c>
       <c r="U14" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V14" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>470.26400000000001</v>
       </c>
       <c r="W14" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>471.79200000000003</v>
       </c>
       <c r="X14" s="16">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>542.53899999999999</v>
       </c>
       <c r="Y14" s="16">
-        <f t="shared" ref="Y14:AA14" si="20">+Y12+Y13</f>
+        <f t="shared" ref="Y14:AA14" si="21">+Y12+Y13</f>
         <v>491.91899999999998</v>
       </c>
       <c r="Z14" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>595.50800000000004</v>
       </c>
       <c r="AA14" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>505.07100000000003</v>
       </c>
       <c r="AB14" s="16">
-        <f t="shared" ref="AB14:AE14" si="21">+AB12+AB13</f>
+        <f t="shared" ref="AB14:AH14" si="22">+AB12+AB13</f>
         <v>646.93499999999995</v>
       </c>
       <c r="AC14" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>680.8900000000001</v>
       </c>
       <c r="AD14" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>697.5920000000001</v>
       </c>
       <c r="AE14" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>687.41699999999992</v>
       </c>
-      <c r="AF14" s="16"/>
-      <c r="AG14" s="16"/>
-      <c r="AH14" s="16"/>
-      <c r="AR14" s="16">
-        <f t="shared" ref="AR14:AW14" si="22">+AR12+AR13</f>
-        <v>0</v>
-      </c>
-      <c r="AS14" s="16">
+      <c r="AF14" s="16">
+        <f t="shared" si="22"/>
+        <v>674.43100000000004</v>
+      </c>
+      <c r="AG14" s="16">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="AT14" s="16">
+      <c r="AH14" s="16">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
+      <c r="AR14" s="16">
+        <f t="shared" ref="AR14:AW14" si="23">+AR12+AR13</f>
+        <v>0</v>
+      </c>
+      <c r="AS14" s="16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AT14" s="16">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="AU14" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2101.7579999999998</v>
       </c>
       <c r="AV14" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2530.4880000000003</v>
       </c>
       <c r="AW14" s="16">
-        <f t="shared" si="22"/>
-        <v>687.41699999999992</v>
+        <f t="shared" si="23"/>
+        <v>1361.848</v>
       </c>
     </row>
     <row r="15" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3029,123 +3061,132 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
       <c r="I15" s="16">
-        <f t="shared" ref="I15:R15" si="23">+I11-I14</f>
+        <f t="shared" ref="I15:R15" si="24">+I11-I14</f>
         <v>-225.19899999999998</v>
       </c>
       <c r="J15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-194.22200000000001</v>
       </c>
       <c r="K15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-186.25400000000002</v>
       </c>
       <c r="L15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-146.15999999999997</v>
       </c>
       <c r="M15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-181.67700000000002</v>
       </c>
       <c r="N15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-194.56099999999998</v>
       </c>
       <c r="O15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-146.73200000000003</v>
       </c>
       <c r="P15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-191.68600000000001</v>
       </c>
       <c r="Q15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-253.43100000000004</v>
       </c>
       <c r="R15" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-19.995090000000033</v>
       </c>
       <c r="S15" s="16">
-        <f t="shared" ref="S15:X15" si="24">+S11-S14</f>
+        <f t="shared" ref="S15:X15" si="25">+S11-S14</f>
         <v>80.761999999999944</v>
       </c>
       <c r="T15" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-229.83100000000007</v>
       </c>
       <c r="U15" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>313.15300000000002</v>
       </c>
       <c r="V15" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-116.404</v>
       </c>
       <c r="W15" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-43.435000000000002</v>
       </c>
       <c r="X15" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-158.81499999999994</v>
       </c>
       <c r="Y15" s="16">
-        <f t="shared" ref="Y15:AA15" si="25">+Y11-Y14</f>
+        <f t="shared" ref="Y15:AA15" si="26">+Y11-Y14</f>
         <v>-76.904999999999973</v>
       </c>
       <c r="Z15" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-103.99000000000001</v>
       </c>
       <c r="AA15" s="16">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>18.396999999999935</v>
       </c>
       <c r="AB15" s="16">
-        <f t="shared" ref="AB15:AE15" si="26">+AB11-AB14</f>
+        <f t="shared" ref="AB15:AH15" si="27">+AB11-AB14</f>
         <v>-16.198999999999955</v>
       </c>
       <c r="AC15" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>367.98199999999997</v>
       </c>
       <c r="AD15" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>131.71800000000007</v>
       </c>
       <c r="AE15" s="16">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>268.63599999999997</v>
       </c>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="16"/>
+      <c r="AF15" s="16">
+        <f t="shared" si="27"/>
+        <v>318.0659999999998</v>
+      </c>
+      <c r="AG15" s="16">
+        <f t="shared" si="27"/>
+        <v>1000.8429999999998</v>
+      </c>
+      <c r="AH15" s="16">
+        <f t="shared" si="27"/>
+        <v>1074.752</v>
+      </c>
       <c r="AR15" s="16">
-        <f t="shared" ref="AR15:AW15" si="27">+AR11-AR14</f>
+        <f t="shared" ref="AR15:AW15" si="28">+AR11-AR14</f>
         <v>0</v>
       </c>
       <c r="AS15" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>805.30490999999984</v>
       </c>
       <c r="AT15" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>833.53123499999992</v>
       </c>
       <c r="AU15" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-383.14499999999953</v>
       </c>
       <c r="AV15" s="16">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>501.89800000000014</v>
       </c>
       <c r="AW15" s="16">
-        <f t="shared" si="27"/>
-        <v>4016.7829999999999</v>
+        <f t="shared" si="28"/>
+        <v>2662.2969999999987</v>
       </c>
     </row>
     <row r="16" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3259,100 +3300,109 @@
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
       <c r="I17" s="16">
-        <f t="shared" ref="I17:AE17" si="28">+I15+I16</f>
+        <f t="shared" ref="I17:AH17" si="29">+I15+I16</f>
         <v>-252.44899999999998</v>
       </c>
       <c r="J17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-243.59900000000002</v>
       </c>
       <c r="K17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-199.27500000000001</v>
       </c>
       <c r="L17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-188.33099999999996</v>
       </c>
       <c r="M17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-204.23600000000002</v>
       </c>
       <c r="N17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-260.30200000000002</v>
       </c>
       <c r="O17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-239.35600000000002</v>
       </c>
       <c r="P17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-274.673</v>
       </c>
       <c r="Q17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-324.74800000000005</v>
       </c>
       <c r="R17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-19.995090000000033</v>
       </c>
       <c r="S17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>80.761999999999944</v>
       </c>
       <c r="T17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-274.20900000000006</v>
       </c>
       <c r="U17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>313.15300000000002</v>
       </c>
       <c r="V17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-117.336</v>
       </c>
       <c r="W17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-43.435000000000002</v>
       </c>
       <c r="X17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-218.59599999999995</v>
       </c>
       <c r="Y17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-79.134999999999962</v>
       </c>
       <c r="Z17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-111.94200000000001</v>
       </c>
       <c r="AA17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-41.276000000000067</v>
       </c>
       <c r="AB17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-28.958999999999957</v>
       </c>
       <c r="AC17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>352.26499999999999</v>
       </c>
       <c r="AD17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>92.948000000000064</v>
       </c>
       <c r="AE17" s="16">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>225.94799999999998</v>
       </c>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="16"/>
+      <c r="AF17" s="16">
+        <f t="shared" si="29"/>
+        <v>318.0659999999998</v>
+      </c>
+      <c r="AG17" s="16">
+        <f t="shared" si="29"/>
+        <v>1000.8429999999998</v>
+      </c>
+      <c r="AH17" s="16">
+        <f t="shared" si="29"/>
+        <v>1074.752</v>
+      </c>
       <c r="AU17" s="2">
         <f>+AU15+AU16</f>
         <v>-453.10799999999949</v>
@@ -3363,7 +3413,7 @@
       </c>
       <c r="AW17" s="2">
         <f>+AW15+AW16</f>
-        <v>3974.0949999999998</v>
+        <v>2619.6089999999986</v>
       </c>
     </row>
     <row r="18" spans="2:49" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3458,47 +3508,47 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
       <c r="I19" s="16">
-        <f t="shared" ref="I19:S19" si="29">+I17-I18</f>
+        <f t="shared" ref="I19:S19" si="30">+I17-I18</f>
         <v>-253.28799999999998</v>
       </c>
       <c r="J19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-243.54000000000002</v>
       </c>
       <c r="K19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-200.291</v>
       </c>
       <c r="L19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-187.10299999999995</v>
       </c>
       <c r="M19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-204.51400000000001</v>
       </c>
       <c r="N19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-258.46000000000004</v>
       </c>
       <c r="O19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-240.34100000000004</v>
       </c>
       <c r="P19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-277.40199999999999</v>
       </c>
       <c r="Q19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-324.74800000000005</v>
       </c>
       <c r="R19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-19.995090000000033</v>
       </c>
       <c r="S19" s="16">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>80.761999999999944</v>
       </c>
       <c r="T19" s="2">
@@ -3522,32 +3572,44 @@
         <v>-224.31799999999996</v>
       </c>
       <c r="Y19" s="2">
-        <f t="shared" ref="Y19:AE19" si="30">+Y17-Y18</f>
+        <f t="shared" ref="Y19:AH19" si="31">+Y17-Y18</f>
         <v>-79.134999999999962</v>
       </c>
       <c r="Z19" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-111.94200000000001</v>
       </c>
       <c r="AA19" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-41.276000000000067</v>
       </c>
       <c r="AB19" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-28.958999999999957</v>
       </c>
       <c r="AC19" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>352.26499999999999</v>
       </c>
       <c r="AD19" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>92.948000000000064</v>
       </c>
       <c r="AE19" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>210.28599999999997</v>
+      </c>
+      <c r="AF19" s="2">
+        <f t="shared" si="31"/>
+        <v>318.0659999999998</v>
+      </c>
+      <c r="AG19" s="2">
+        <f t="shared" si="31"/>
+        <v>1000.8429999999998</v>
+      </c>
+      <c r="AH19" s="2">
+        <f t="shared" si="31"/>
+        <v>1074.752</v>
       </c>
       <c r="AU19" s="2">
         <f>+AU17-AU18</f>
@@ -3559,7 +3621,7 @@
       </c>
       <c r="AW19" s="2">
         <f>+AW17-AW18</f>
-        <v>3958.433</v>
+        <v>2603.9469999999988</v>
       </c>
     </row>
     <row r="20" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3573,60 +3635,60 @@
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
       <c r="I20" s="15">
-        <f t="shared" ref="I20:T20" si="31">+I19/I21</f>
+        <f t="shared" ref="I20:T20" si="32">+I19/I21</f>
         <v>-2.1837808011311708</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2.094535321740028</v>
       </c>
       <c r="K20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1.710719166381961</v>
       </c>
       <c r="L20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1.5886883130115812</v>
       </c>
       <c r="M20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1.7165711216122075</v>
       </c>
       <c r="N20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2.1579153899459813</v>
       </c>
       <c r="O20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1.9963037718139762</v>
       </c>
       <c r="P20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2.2945506881948119</v>
       </c>
       <c r="Q20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2.6582518867770086</v>
       </c>
       <c r="R20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-0.16367147978979449</v>
       </c>
       <c r="S20" s="15"/>
       <c r="T20" s="15">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2.2142324260582873</v>
       </c>
       <c r="V20" s="15">
-        <f t="shared" ref="V20:Y20" si="32">+V19/V21</f>
+        <f t="shared" ref="V20:Y20" si="33">+V19/V21</f>
         <v>-0.93410713859234318</v>
       </c>
       <c r="X20" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-1.7700046554567472</v>
       </c>
       <c r="Y20" s="15">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-0.61540555253130069</v>
       </c>
       <c r="Z20" s="1">
@@ -3642,16 +3704,28 @@
         <v>-0.22169060232109472</v>
       </c>
       <c r="AC20" s="1">
-        <f t="shared" ref="AC20:AE20" si="33">+AC19/AC21</f>
+        <f t="shared" ref="AC20:AH20" si="34">+AC19/AC21</f>
         <v>2.5647625010921162</v>
       </c>
       <c r="AD20" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.68203197804536264</v>
       </c>
       <c r="AE20" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.5430324109743836</v>
+      </c>
+      <c r="AF20" s="1">
+        <f t="shared" si="34"/>
+        <v>2.3338983423954902</v>
+      </c>
+      <c r="AG20" s="1">
+        <f t="shared" si="34"/>
+        <v>7.3439657765939481</v>
+      </c>
+      <c r="AH20" s="1">
+        <f t="shared" si="34"/>
+        <v>7.8862937606856418</v>
       </c>
       <c r="AU20" s="1">
         <f>+AU19/AU21</f>
@@ -3663,7 +3737,7 @@
       </c>
       <c r="AW20" s="1">
         <f>+AW19/AW21</f>
-        <v>29.046110609696139</v>
+        <v>19.107190290649456</v>
       </c>
     </row>
     <row r="21" spans="2:49" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3736,6 +3810,18 @@
       </c>
       <c r="AE21" s="2">
         <f>+AD21</f>
+        <v>136.28100000000001</v>
+      </c>
+      <c r="AF21" s="2">
+        <f>+AE21</f>
+        <v>136.28100000000001</v>
+      </c>
+      <c r="AG21" s="2">
+        <f>+AF21</f>
+        <v>136.28100000000001</v>
+      </c>
+      <c r="AH21" s="2">
+        <f>+AG21</f>
         <v>136.28100000000001</v>
       </c>
       <c r="AU21" s="2">
@@ -3766,15 +3852,15 @@
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
       <c r="M23" s="20">
-        <f t="shared" ref="M23:O23" si="34">+M9/I9-1</f>
+        <f t="shared" ref="M23:O23" si="35">+M9/I9-1</f>
         <v>0.49089016551055575</v>
       </c>
       <c r="N23" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.58065443073574574</v>
       </c>
       <c r="O23" s="20">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.20101258123739907</v>
       </c>
       <c r="P23" s="20">
@@ -3782,76 +3868,76 @@
         <v>1.9337755550820068E-2</v>
       </c>
       <c r="Q23" s="20">
-        <f t="shared" ref="Q23:Z23" si="35">+Q9/M9-1</f>
+        <f t="shared" ref="Q23:Z23" si="36">+Q9/M9-1</f>
         <v>0.40863280979358652</v>
       </c>
       <c r="R23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5.9643761966463593E-3</v>
       </c>
       <c r="S23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.49719355337875504</v>
       </c>
       <c r="T23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.41783131243939509</v>
       </c>
       <c r="U23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.1848123008936613</v>
       </c>
       <c r="V23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.69072236299249856</v>
       </c>
       <c r="W23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.54822575088477588</v>
       </c>
       <c r="X23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.4192637582587202</v>
       </c>
       <c r="Y23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.59959827943529187</v>
       </c>
       <c r="Z23" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.3516276340745661</v>
       </c>
       <c r="AA23" s="20">
-        <f t="shared" ref="AA23" si="36">+AA9/W9-1</f>
+        <f t="shared" ref="AA23" si="37">+AA9/W9-1</f>
         <v>0.200913149637997</v>
       </c>
       <c r="AB23" s="20">
-        <f t="shared" ref="AB23" si="37">+AB9/X9-1</f>
+        <f t="shared" ref="AB23" si="38">+AB9/X9-1</f>
         <v>0.71020300798415525</v>
       </c>
       <c r="AC23" s="20">
-        <f t="shared" ref="AC23" si="38">+AC9/Y9-1</f>
+        <f t="shared" ref="AC23" si="39">+AC9/Y9-1</f>
         <v>1.4934690039707021</v>
       </c>
       <c r="AD23" s="20">
-        <f t="shared" ref="AD23:AH23" si="39">+AD9/Z9-1</f>
+        <f t="shared" ref="AD23:AH23" si="40">+AD9/Z9-1</f>
         <v>0.84581591190153715</v>
       </c>
       <c r="AE23" s="20">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.96609624173125286</v>
       </c>
       <c r="AF23" s="20">
-        <f t="shared" si="39"/>
-        <v>0.5362891290945071</v>
+        <f t="shared" si="40"/>
+        <v>0.66856191570514767</v>
       </c>
       <c r="AG23" s="20">
-        <f t="shared" si="39"/>
-        <v>-4.9734753319786718E-3</v>
+        <f t="shared" si="40"/>
+        <v>4.0245759495799005E-2</v>
       </c>
       <c r="AH23" s="20">
-        <f t="shared" si="39"/>
-        <v>0.20025833315861963</v>
+        <f t="shared" si="40"/>
+        <v>0.25174265496115411</v>
       </c>
       <c r="AT23" s="26">
         <f>+AT9/AS9-1</f>
@@ -3867,7 +3953,7 @@
       </c>
       <c r="AW23" s="26">
         <f>+AW9/AV9-1</f>
-        <v>0.3236719242936188</v>
+        <v>0.38165061174411874</v>
       </c>
     </row>
     <row r="24" spans="2:49" x14ac:dyDescent="0.25">
@@ -3879,124 +3965,124 @@
         <v>0.8268058766974169</v>
       </c>
       <c r="J24" s="19">
-        <f t="shared" ref="J24:Z24" si="40">+J11/J9</f>
+        <f t="shared" ref="J24:Z24" si="41">+J11/J9</f>
         <v>0.85923380736356858</v>
       </c>
       <c r="K24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.8250678620907157</v>
       </c>
       <c r="L24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.82428259874043885</v>
       </c>
       <c r="M24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.82592081350295521</v>
       </c>
       <c r="N24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.85431759723054912</v>
       </c>
       <c r="O24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.83294022761055797</v>
       </c>
       <c r="P24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.81848428506614246</v>
       </c>
       <c r="Q24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.86187600735511105</v>
       </c>
       <c r="R24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.83</v>
       </c>
       <c r="S24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.82815308966770007</v>
       </c>
       <c r="T24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.73217590994936532</v>
       </c>
       <c r="U24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
       <c r="V24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.80474303985736317</v>
       </c>
       <c r="W24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.86653531121733729</v>
       </c>
       <c r="X24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.8482037860635373</v>
       </c>
       <c r="Y24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.828505207428746</v>
       </c>
       <c r="Z24" s="19">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.82700497194343259</v>
       </c>
       <c r="AA24" s="19">
-        <f t="shared" ref="AA24:AH24" si="41">+AA11/AA9</f>
+        <f t="shared" ref="AA24:AH24" si="42">+AA11/AA9</f>
         <v>0.8817773405586784</v>
       </c>
       <c r="AB24" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.81523196012868226</v>
       </c>
       <c r="AC24" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.83975193470752407</v>
       </c>
       <c r="AD24" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.75595720456905136</v>
       </c>
       <c r="AE24" s="19">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.8191170989783022</v>
       </c>
       <c r="AF24" s="19">
-        <f t="shared" si="41"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>0.76881253156594997</v>
       </c>
       <c r="AG24" s="19">
-        <f t="shared" si="41"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>0.77029756159883744</v>
       </c>
       <c r="AH24" s="19">
-        <f t="shared" si="41"/>
-        <v>0</v>
+        <f t="shared" si="42"/>
+        <v>0.78266068454554782</v>
       </c>
       <c r="AS24" s="19">
-        <f t="shared" ref="AS24:AW24" si="42">+AS11/AS9</f>
+        <f t="shared" ref="AS24:AW24" si="43">+AS11/AS9</f>
         <v>0.83671519855370602</v>
       </c>
       <c r="AT24" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.83</v>
       </c>
       <c r="AU24" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.84163923010132802</v>
       </c>
       <c r="AV24" s="19">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.81660656449791691</v>
       </c>
       <c r="AW24" s="19">
-        <f t="shared" si="42"/>
-        <v>0.95704818524605295</v>
+        <f t="shared" si="43"/>
+        <v>0.78433892979795805</v>
       </c>
     </row>
   </sheetData>
